--- a/Games/Codes/Dialogues/NeuralRust_Dialogue.xlsx
+++ b/Games/Codes/Dialogues/NeuralRust_Dialogue.xlsx
@@ -25,24 +25,411 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="257">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="257">
+  <x:si>
+    <x:t>푸른 곰팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 파라미터 커스텀: shake_char:intensity=5,duration=300  (기본값 사용 시 예약어만 입력)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 배경 태그 → 파일명 매핑  |  파일명은 확장자 제외, Assets/Sprites/Backgrounds/ 경로 기준</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// fx 컬럼에 예약어 입력  |  복합(Y끼리만): shake_screen|fade_out_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 태그는 대사 시트 bg 컬럼에 입력  |  공백=이전 배경 유지  |  NONE=배경 제거  |  전환 접두어: instant:A  fade_black:B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// sfx: SFX 탭 별칭 (복합: Happy|Beep)  |  fx: FX 탭 예약어 (복합: shake_char|fade_out, 파라미터: shake_char:intensity=5)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// BGM 없는 이벤트는 행 비워두기  |  같은 BGM 유지 시 동일 파일명 복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// P : Player 고정 — 수정 불가  |  단축어는 대사 시트 char 컬럼에 입력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// target — screen: 카메라  |  char: 현재 발화 캐릭터  |  ui: 대화창  |  all: 전체</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// goto: 같은 시트 line_id | END | 다음 시트명  |  숫자 ID도 텍스트 서식으로 처리됨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 표정: b001 → Character_[캐릭터명]_001 자동 매핑  |  expr 공백 = 이전 표정 유지</x:t>
+  </x:si>
   <x:si>
     <x:t>// char: CAST 탭 단축어 (P 고정)  |  expr: 001~999, 공백=이전 표정 유지  |  choice: 1=선택지 줄</x:t>
   </x:si>
   <x:si>
-    <x:t>// sfx: SFX 탭 별칭 (복합: Happy|Beep)  |  fx: FX 탭 예약어 (복합: shake_char|fade_out, 파라미터: shake_char:intensity=5)</x:t>
+    <x:t>왼쪽에서 슬라이드 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 강조 확대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체 암전 후 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체 화이트아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>flash_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외곽 지부 - 외부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phaser3 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fade_out</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외곽 지부 - 복도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 페이드 아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bounce_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면 페이드 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_confirm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면 전체 진동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발화 캐릭터만 진동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>blackout</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pause_text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이핑 속도 배속</x:t>
+  </x:si>
+  <x:si>
+    <x:t>speed=0.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면 순간 번쩍</x:t>
+  </x:si>
+  <x:si>
+    <x:t>//관리자 캐릭터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>whiteout</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화창 페이드 아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[DIALOGUE]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그걸 왜 물어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>flag_set</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zoom_out</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내일도 잘 부탁해요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 미안해요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>player_rude</x:t>
+  </x:si>
+  <x:si>
+    <x:t>flag_check</x:t>
+  </x:si>
+  <x:si>
+    <x:t>slow_text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pan_camera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 페이드 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tint_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>day1_1_done</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shop_Open</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[ CAST ]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화창 페이드 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>shake_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>repeat=2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 닉네임: 비어있으면 캐릭터명 사용  |  ???처럼 미공개명 가능  |  런타임 변경: SaveManager.setFlag('cast_nick_A', 'Noa')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음. . . 뭐, 상관 없나.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>textbox_fade_out</x:t>
+  </x:si>
+  <x:si>
+    <x:t>── 화면 전체 (screen)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scene_transition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>── 대화창 / UI (ui)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 인수인계를 시작하겠습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bgm_calm_morning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 색조 (분노/상태이상)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이핑 일시 정지 (극적 침묵)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천천히 배우면 될 거라 생각합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>── 캐릭터 단독 (char)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상점 입장 (동일 유지 시 복사)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: alpha 0↔1, yoyo, repeat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fadeOut → onComplete: 다음 시트 로드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.fadeOut → alpha 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 복합 사용: Happy|Door  처럼 | 로 구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sprite.setTint → clearTint()</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: scaleX/Y→scale, yoyo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저는 외곽 지부에 이전 관리자 노아(Noa)라고 합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말 그대로 외각 지부입니다, 별 볼 일 없는 곳이죠.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.zoomTo(zoom, dur)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메모</x:t>
+  </x:si>
+  <x:si>
+    <x:t>003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단축어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F</x:t>
+  </x:si>
+  <x:si>
+    <x:t>030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>I</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ui</x:t>
+  </x:si>
+  <x:si>
+    <x:t>005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>END</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H</x:t>
+  </x:si>
+  <x:si>
+    <x:t>020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Noa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복합</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D</x:t>
+  </x:si>
+  <x:si>
+    <x:t>노아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>G</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>all</x:t>
+  </x:si>
+  <x:si>
+    <x:t>009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예약어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_cancel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면 페이드 아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_sad_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sprite.x+=dist; tweens: x-=dist, alpha→1</x:t>
   </x:si>
   <x:si>
     <x:t>sprite.x-=dist; tweens: x+=dist, alpha→1</x:t>
   </x:si>
   <x:si>
-    <x:t>sprite.x+=dist; tweens: x-=dist, alpha→1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 태그는 대사 시트 bg 컬럼에 입력  |  공백=이전 배경 유지  |  NONE=배경 제거  |  전환 접두어: instant:A  fade_black:B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// target — screen: 카메라  |  char: 현재 발화 캐릭터  |  ui: 대화창  |  all: 전체</x:t>
+    <x:t>아무튼, 새롭게 외각 지부 관리자로 부임하신 것을 축하드립니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.fadeOut(dur, r, g, b)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 별칭을 대사 시트 sfx 컬럼에 입력 — 파일명 자동 매핑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogManager.pauseTyping(duration)</x:t>
   </x:si>
   <x:si>
     <x:t>cameras.main.shake(dur, intensity)</x:t>
@@ -51,751 +438,364 @@
     <x:t>cameras.main.fadeIn(dur, r, g, b)</x:t>
   </x:si>
   <x:si>
+    <x:t>tweens: x ±intensity, yoyo, repeat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.flash(dur, r, g, b)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: dialogBox alpha 0.2→1, yoyo</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogManager.setTypingSpeed(speed)</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogBox.setAlpha(0); tweens: alpha→1</x:t>
+  </x:si>
+  <x:si>
     <x:t>tweens: dialogBox x ±intensity, yoyo</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogBox.setAlpha(0); tweens: alpha→1</x:t>
+    <x:t>cameras.main.flash(dur, 255,255,255)</x:t>
   </x:si>
   <x:si>
     <x:t>tweens: y-=height, yoyo, ease:Bounce</x:t>
   </x:si>
   <x:si>
-    <x:t>cameras.main.flash(dur, 255,255,255)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// fx 컬럼에 예약어 입력  |  복합(Y끼리만): shake_screen|fade_out_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 파라미터 커스텀: shake_char:intensity=5,duration=300  (기본값 사용 시 예약어만 입력)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 배경 태그 → 파일명 매핑  |  파일명은 확장자 제외, Assets/Sprites/Backgrounds/ 경로 기준</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// BGM 없는 이벤트는 행 비워두기  |  같은 BGM 유지 시 동일 파일명 복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// P : Player 고정 — 수정 불가  |  단축어는 대사 시트 char 컬럼에 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 닉네임: 비어있으면 캐릭터명 사용  |  ???처럼 미공개명 가능  |  런타임 변경: SaveManager.setFlag('cast_nick_A', 'Noa')</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bounce_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면 페이드 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 표정: b001 → Character_[캐릭터명]_001 자동 매핑  |  expr 공백 = 이전 표정 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// goto: 같은 시트 line_id | END | 다음 시트명  |  숫자 ID도 텍스트 서식으로 처리됨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>외곽 지부 - 외부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>외곽 지부 - 복도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>외곽 지부 - 사무실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.fadeOut → alpha 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: alpha 0↔1, yoyo, repeat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말 그대로 외각 지부입니다, 별 볼 일 없는 곳이죠.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.zoomTo(zoom, dur)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 복합 사용: Happy|Door  처럼 | 로 구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sprite.setTint → clearTint()</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저는 외곽 지부에 이전 관리자 노아(Noa)라고 합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: scaleX/Y→scale, yoyo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fadeOut → onComplete: 다음 시트 로드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면 전체 진동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 페이드 아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fade_out</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_confirm</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phaser3 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>speed=0.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이핑 속도 배속</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대화창 페이드 아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면 순간 번쩍</x:t>
-  </x:si>
-  <x:si>
-    <x:t>whiteout</x:t>
-  </x:si>
-  <x:si>
-    <x:t>발화 캐릭터만 진동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>//관리자 캐릭터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>pause_text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>blackout</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[DIALOGUE]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그걸 왜 물어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>flag_set</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내일도 잘 부탁해요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>slow_text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 미안해요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>day1_1_done</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shop_Open</x:t>
-  </x:si>
-  <x:si>
-    <x:t>player_rude</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[ CAST ]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>flag_check</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zoom_out</x:t>
-  </x:si>
-  <x:si>
-    <x:t>repeat=2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>pan_camera</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대화창 페이드 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 페이드 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tint_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>shake_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체 암전 후 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>왼쪽에서 슬라이드 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체 화이트아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 강조 확대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>flash_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_sad_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_cancel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면 페이드 아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.fadeOut(dur, r, g, b)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무튼, 새롭게 외각 지부 관리자로 부임하신 것을 축하드립니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: x ±intensity, yoyo, repeat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: dialogBox alpha 0.2→1, yoyo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.flash(dur, r, g, b)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 별칭을 대사 시트 sfx 컬럼에 입력 — 파일명 자동 매핑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogManager.pauseTyping(duration)</x:t>
-  </x:si>
-  <x:si>
     <x:t>BGM 파일명</x:t>
   </x:si>
   <x:si>
+    <x:t>expr</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UI 취소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SFX 파일명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Happy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문 열림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[ BG ]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>choice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반갑습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zoom_in</x:t>
+  </x:si>
+  <x:si>
+    <x:t>씬 전환 연출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경 파일명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬픈 반응</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shop_In</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상점 해금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>line_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>screen</x:t>
+  </x:si>
+  <x:si>
+    <x:t>target</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카메라 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부임이라니?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Beep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shock</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그저 그랬어.</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cancel</x:t>
   </x:si>
   <x:si>
-    <x:t>상점 해금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬픈 반응</x:t>
+    <x:t>대화창 진동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외곽 지부?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Door</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시스템 알림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이벤트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[ FX ]</x:t>
   </x:si>
   <x:si>
     <x:t>타이핑 루프</x:t>
   </x:si>
   <x:si>
-    <x:t>씬 전환 연출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부임이라니?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반갑습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대화창 진동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SFX 파일명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>screen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Beep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이벤트 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UI 취소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shock</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시스템 알림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[ FX ]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Happy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Door</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문 열림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>expr</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그저 그랬어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zoom_in</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카메라 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>line_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[ BG ]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>외곽 지부?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>choice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경 파일명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shop_In</x:t>
-  </x:si>
-  <x:si>
-    <x:t>target</x:t>
+    <x:t>[ SFX ]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fade_in</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 바운스</x:t>
   </x:si>
   <x:si>
     <x:t>카메라 줌 인</x:t>
   </x:si>
   <x:si>
+    <x:t>[ BGM ]</x:t>
+  </x:si>
+  <x:si>
     <x:t>대화창 번쩍</x:t>
   </x:si>
   <x:si>
+    <x:t>Day_1_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Player</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기쁜 반응</x:t>
+  </x:si>
+  <x:si>
+    <x:t>goto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Confirm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1일차 시작</x:t>
+  </x:si>
+  <x:si>
     <x:t>speed=2</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 바운스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Player</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Day_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[ BGM ]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[ SFX ]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터명</x:t>
+    <x:t>충격/놀람</x:t>
   </x:si>
   <x:si>
     <x:t>기본 파라미터</x:t>
   </x:si>
   <x:si>
-    <x:t>goto</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fade_in</x:t>
-  </x:si>
-  <x:si>
     <x:t>Typing</x:t>
   </x:si>
   <x:si>
     <x:t>UI 확인</x:t>
   </x:si>
   <x:si>
-    <x:t>Confirm</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1일차 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>충격/놀람</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기쁜 반응</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T</x:t>
-  </x:si>
-  <x:si>
-    <x:t>003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>I</x:t>
-  </x:si>
-  <x:si>
-    <x:t>002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메모</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P</x:t>
-  </x:si>
-  <x:si>
-    <x:t>030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단축어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>G</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예약어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ui</x:t>
-  </x:si>
-  <x:si>
-    <x:t>all</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Noa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>노아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복합</x:t>
-  </x:si>
-  <x:si>
-    <x:t>005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Q</x:t>
-  </x:si>
-  <x:si>
-    <x:t>006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>END</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bgm_calm_morning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>textbox_fade_out</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이핑 일시 정지 (극적 침묵)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 인수인계를 시작하겠습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상점 입장 (동일 유지 시 복사)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음. . . 뭐, 상관 없나.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 색조 (분노/상태이상)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>── 화면 전체 (screen)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천천히 배우면 될 거라 생각합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>── 캐릭터 단독 (char)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>── 대화창 / UI (ui)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scene_transition</x:t>
+    <x:t>intensity=5, duration=300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>color=ffffff, duration=200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scale=1.15, duration=200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>intensity=3, duration=300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: x-=dist, alpha→0</x:t>
   </x:si>
   <x:si>
     <x:t>tweens: dialogBox alpha→0</x:t>
   </x:si>
   <x:si>
-    <x:t>intensity=3, duration=300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: x-=dist, alpha→0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>color=ffffff, duration=200</x:t>
-  </x:si>
-  <x:si>
     <x:t>// 이벤트 시트명과 동일하게 작성 — 자동 매핑</x:t>
   </x:si>
   <x:si>
-    <x:t>intensity=5, duration=300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scale=1.15, duration=200</x:t>
+    <x:t>duration=300, distance=200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>intensity=3, duration=200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 플레이어 고정 — 초상화 없음, 수정 불가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duration=400, color=000000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: x+=dist, alpha→0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>color=ff4444, duration=200</x:t>
   </x:si>
   <x:si>
     <x:t>cameras.main.pan(x, y, dur)</x:t>
   </x:si>
   <x:si>
-    <x:t>// 플레이어 고정 — 초상화 없음, 수정 불가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duration=300, distance=200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>color=ff4444, duration=200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duration=400, color=000000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: x+=dist, alpha→0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>intensity=3, duration=200</x:t>
-  </x:si>
-  <x:si>
     <x:t>sfx_door_open</x:t>
   </x:si>
   <x:si>
+    <x:t>그렇군요... 잘 쉬세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카메라 줌 아웃 (원복)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_happy_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: alpha→1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duration=300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_shock_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이벤트 ID (시트명)</x:t>
+  </x:si>
+  <x:si>
     <x:t>별칭 (sfx 컬럼에 입력)</x:t>
   </x:si>
   <x:si>
+    <x:t>flash_screen</x:t>
+  </x:si>
+  <x:si>
     <x:t>bgm_shop_theme</x:t>
   </x:si>
   <x:si>
-    <x:t>이벤트 ID (시트명)</x:t>
+    <x:t>slide_in_right</x:t>
   </x:si>
   <x:si>
     <x:t>duration=250</x:t>
   </x:si>
   <x:si>
-    <x:t>sfx_shock_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duration=300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렇군요... 잘 쉬세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카메라 줌 아웃 (원복)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>flash_screen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: alpha→1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>slide_in_right</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_happy_001</x:t>
+    <x:t>닉네임 (대화창 표시명)</x:t>
   </x:si>
   <x:si>
     <x:t>duration=150</x:t>
   </x:si>
   <x:si>
+    <x:t>slide_in_left</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_beep_alert</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fade_in_char</x:t>
+  </x:si>
+  <x:si>
     <x:t>sfx_typing_loop</x:t>
   </x:si>
   <x:si>
+    <x:t>speed_up_text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 왼쪽 슬라이드 아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>textbox_flash</x:t>
+  </x:si>
+  <x:si>
+    <x:t>shake_screen</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 오른쪽 슬라이드 아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오른쪽에서 슬라이드 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: alpha→0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>slide_out_right</x:t>
+  </x:si>
+  <x:si>
     <x:t>fade_out_char</x:t>
   </x:si>
   <x:si>
-    <x:t>닉네임 (대화창 표시명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>speed_up_text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>textbox_flash</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 왼쪽 슬라이드 아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>slide_in_left</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_beep_alert</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fade_in_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>shake_screen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 오른쪽 슬라이드 아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오른쪽에서 슬라이드 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: alpha→0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>slide_out_right</x:t>
+    <x:t>── 전체 동시 (all)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Background003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 번쩍 (피격/강조)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Background002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duration=500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scale_up_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>textbox_shake</x:t>
+  </x:si>
+  <x:si>
+    <x:t>slide_out_left</x:t>
   </x:si>
   <x:si>
     <x:t>타이핑 속도 감속 (강조)</x:t>
   </x:si>
   <x:si>
-    <x:t>slide_out_left</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duration=500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Background003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scale_up_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 번쩍 (피격/강조)</x:t>
-  </x:si>
-  <x:si>
     <x:t>오늘 하루는 어떠셨나요?</x:t>
   </x:si>
   <x:si>
-    <x:t>textbox_shake</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Background002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>── 전체 동시 (all)</x:t>
-  </x:si>
-  <x:si>
     <x:t>태그 (bg 컬럼에 입력)</x:t>
   </x:si>
   <x:si>
     <x:t>textbox_fade_in</x:t>
   </x:si>
   <x:si>
-    <x:t>Background001</x:t>
+    <x:t>이런, 아무것도 기억나지 않으신가보네요.</x:t>
   </x:si>
   <x:si>
     <x:t>height=20, duration=400</x:t>
   </x:si>
   <x:si>
+    <x:t>//관리자 캐릭터가 이름을 공개하기 이전.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zoom=1.2, duration=300</x:t>
+  </x:si>
+  <x:si>
     <x:t>x=0, y=0, duration=500</x:t>
   </x:si>
   <x:si>
-    <x:t>//관리자 캐릭터가 이름을 공개하기 이전.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이런, 아무것도 기억나지 않으신가보네요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zoom=1.2, duration=300</x:t>
-  </x:si>
-  <x:si>
     <x:t>zoom=1.0, duration=300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Background_003</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3511,17 +3511,17 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="19.25">
       <x:c r="A1" s="135" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B1" s="136"/>
       <x:c r="C1" s="137"/>
       <x:c r="D1" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4" ht="16" customHeight="1">
       <x:c r="A2" s="138" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="138"/>
       <x:c r="C2" s="138"/>
@@ -3529,7 +3529,7 @@
     </x:row>
     <x:row r="3" spans="1:4" ht="16" customHeight="1">
       <x:c r="A3" s="138" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="138"/>
       <x:c r="C3" s="138"/>
@@ -3537,61 +3537,61 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="4" t="s">
-        <x:v>149</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>156</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D4" s="6" t="s">
-        <x:v>226</x:v>
+        <x:v>223</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="7" t="s">
-        <x:v>147</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B5" s="8" t="s">
-        <x:v>119</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C5" s="9" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D5" s="9"/>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="10" t="s">
-        <x:v>136</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B6" s="11" t="s">
-        <x:v>172</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C6" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>173</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="13" t="s">
-        <x:v>177</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B7" s="11" t="s">
-        <x:v>172</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
-        <x:v>253</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="D7" s="15" t="s">
-        <x:v>141</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="10" t="s">
-        <x:v>138</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B8" s="11"/>
       <x:c r="C8" s="12"/>
@@ -3599,7 +3599,7 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="13" t="s">
-        <x:v>161</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B9" s="14"/>
       <x:c r="C9" s="15"/>
@@ -3607,7 +3607,7 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="10" t="s">
-        <x:v>162</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B10" s="11"/>
       <x:c r="C10" s="12"/>
@@ -3615,7 +3615,7 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="13" t="s">
-        <x:v>153</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B11" s="14"/>
       <x:c r="C11" s="15"/>
@@ -3623,7 +3623,7 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="10" t="s">
-        <x:v>160</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B12" s="11"/>
       <x:c r="C12" s="12"/>
@@ -3631,7 +3631,7 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="13" t="s">
-        <x:v>158</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B13" s="14"/>
       <x:c r="C13" s="15"/>
@@ -3639,7 +3639,7 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="10" t="s">
-        <x:v>144</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B14" s="11"/>
       <x:c r="C14" s="12"/>
@@ -3647,7 +3647,7 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="13" t="s">
-        <x:v>140</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B15" s="14"/>
       <x:c r="C15" s="15"/>
@@ -3655,7 +3655,7 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="10" t="s">
-        <x:v>137</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B16" s="11"/>
       <x:c r="C16" s="12"/>
@@ -3663,7 +3663,7 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="13" t="s">
-        <x:v>134</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B17" s="14"/>
       <x:c r="C17" s="15"/>
@@ -3671,7 +3671,7 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="10" t="s">
-        <x:v>139</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B18" s="11"/>
       <x:c r="C18" s="12"/>
@@ -3679,7 +3679,7 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="13" t="s">
-        <x:v>159</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B19" s="14"/>
       <x:c r="C19" s="15"/>
@@ -3687,7 +3687,7 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="10" t="s">
-        <x:v>135</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B20" s="11"/>
       <x:c r="C20" s="12"/>
@@ -3695,7 +3695,7 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B21" s="14"/>
       <x:c r="C21" s="15"/>
@@ -3703,7 +3703,7 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="10" t="s">
-        <x:v>179</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B22" s="11"/>
       <x:c r="C22" s="12"/>
@@ -3711,7 +3711,7 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="13" t="s">
-        <x:v>155</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B23" s="14"/>
       <x:c r="C23" s="15"/>
@@ -3719,7 +3719,7 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="10" t="s">
-        <x:v>164</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B24" s="11"/>
       <x:c r="C24" s="12"/>
@@ -3727,7 +3727,7 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="13" t="s">
-        <x:v>142</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B25" s="14"/>
       <x:c r="C25" s="15"/>
@@ -3789,7 +3789,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="19.25">
       <x:c r="A1" s="135" t="s">
-        <x:v>107</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B1" s="136"/>
       <x:c r="C1" s="137"/>
@@ -3797,7 +3797,7 @@
     </x:row>
     <x:row r="2" spans="1:4" ht="16" customHeight="1">
       <x:c r="A2" s="138" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="138"/>
       <x:c r="C2" s="138"/>
@@ -3816,46 +3816,46 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>112</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>156</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="17" t="s">
-        <x:v>136</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B5" s="18" t="s">
-        <x:v>250</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C5" s="19" t="s">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="20" t="s">
-        <x:v>133</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B6" s="21" t="s">
-        <x:v>246</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C6" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="17" t="s">
-        <x:v>138</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B7" s="18" t="s">
-        <x:v>241</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C7" s="19" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
     </x:row>
@@ -3883,7 +3883,7 @@
     <x:mergeCell ref="A2:C2"/>
     <x:mergeCell ref="A3:C3"/>
   </x:mergeCells>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -3903,7 +3903,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="19.25">
       <x:c r="A1" s="135" t="s">
-        <x:v>121</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B1" s="136"/>
       <x:c r="C1" s="137"/>
@@ -3911,7 +3911,7 @@
     </x:row>
     <x:row r="2" spans="1:4" ht="16" customHeight="1">
       <x:c r="A2" s="138" t="s">
-        <x:v>200</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B2" s="138"/>
       <x:c r="C2" s="138"/>
@@ -3919,7 +3919,7 @@
     </x:row>
     <x:row r="3" spans="1:4" ht="16" customHeight="1">
       <x:c r="A3" s="138" t="s">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="138"/>
       <x:c r="C3" s="138"/>
@@ -3927,49 +3927,49 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="16" t="s">
-        <x:v>213</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="s">
-        <x:v>156</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="17" t="s">
-        <x:v>120</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B5" s="18" t="s">
-        <x:v>184</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C5" s="19" t="s">
-        <x:v>130</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="20" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B6" s="21" t="s">
-        <x:v>212</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C6" s="22" t="s">
-        <x:v>84</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="17" t="s">
-        <x:v>113</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B7" s="18" t="s">
-        <x:v>212</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C7" s="19" t="s">
-        <x:v>188</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
     </x:row>
@@ -4377,7 +4377,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="19.25">
       <x:c r="A1" s="135" t="s">
-        <x:v>122</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B1" s="136"/>
       <x:c r="C1" s="137"/>
@@ -4385,7 +4385,7 @@
     </x:row>
     <x:row r="2" spans="1:4" ht="16" customHeight="1">
       <x:c r="A2" s="138" t="s">
-        <x:v>80</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B2" s="138"/>
       <x:c r="C2" s="138"/>
@@ -4393,7 +4393,7 @@
     </x:row>
     <x:row r="3" spans="1:4" ht="16" customHeight="1">
       <x:c r="A3" s="138" t="s">
-        <x:v>30</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B3" s="138"/>
       <x:c r="C3" s="138"/>
@@ -4401,109 +4401,109 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="25" t="s">
-        <x:v>211</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>156</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="26" t="s">
-        <x:v>99</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B5" s="18" t="s">
-        <x:v>222</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C5" s="19" t="s">
-        <x:v>132</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="27" t="s">
-        <x:v>163</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B6" s="21" t="s">
-        <x:v>72</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C6" s="22" t="s">
-        <x:v>85</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="26" t="s">
-        <x:v>96</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B7" s="18" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C7" s="19" t="s">
-        <x:v>131</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="27" t="s">
-        <x:v>100</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B8" s="21" t="s">
         <x:v>210</x:v>
       </x:c>
       <x:c r="C8" s="22" t="s">
-        <x:v>101</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="26" t="s">
-        <x:v>93</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B9" s="18" t="s">
-        <x:v>231</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C9" s="19" t="s">
-        <x:v>97</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="27" t="s">
-        <x:v>127</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B10" s="21" t="s">
-        <x:v>224</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C10" s="22" t="s">
-        <x:v>86</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="26" t="s">
-        <x:v>129</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B11" s="18" t="s">
-        <x:v>38</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C11" s="19" t="s">
-        <x:v>128</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D11" s="3"/>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="27" t="s">
-        <x:v>83</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B12" s="21" t="s">
-        <x:v>73</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C12" s="22" t="s">
-        <x:v>95</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D12" s="3"/>
     </x:row>
@@ -4914,7 +4914,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="19.25">
       <x:c r="A1" s="135" t="s">
-        <x:v>98</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B1" s="136"/>
       <x:c r="C1" s="136"/>
@@ -4924,7 +4924,7 @@
     </x:row>
     <x:row r="2" spans="1:6" ht="16" customHeight="1">
       <x:c r="A2" s="138" t="s">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="138"/>
       <x:c r="C2" s="138"/>
@@ -4934,7 +4934,7 @@
     </x:row>
     <x:row r="3" spans="1:6" ht="16" customHeight="1">
       <x:c r="A3" s="138" t="s">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="138"/>
       <x:c r="C3" s="138"/>
@@ -4944,7 +4944,7 @@
     </x:row>
     <x:row r="4" spans="1:6" ht="16" customHeight="1">
       <x:c r="A4" s="138" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="138"/>
       <x:c r="C4" s="138"/>
@@ -4954,27 +4954,27 @@
     </x:row>
     <x:row r="5" spans="1:6">
       <x:c r="A5" s="30" t="s">
-        <x:v>165</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B5" s="31" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="C5" s="16" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F5" s="32" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="C5" s="16" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="s">
-        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="28" customHeight="1">
       <x:c r="A6" s="139" t="s">
-        <x:v>191</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B6" s="139"/>
       <x:c r="C6" s="139"/>
@@ -4984,22 +4984,22 @@
     </x:row>
     <x:row r="7" spans="1:6" ht="28" customHeight="1">
       <x:c r="A7" s="33" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B7" s="34" t="s">
-        <x:v>92</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C7" s="35" t="s">
-        <x:v>197</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D7" s="36" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E7" s="37" t="s">
-        <x:v>6</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F7" s="38" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6" ht="28" customHeight="1">
@@ -5007,124 +5007,124 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="B8" s="40" t="s">
-        <x:v>92</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C8" s="41" t="s">
-        <x:v>199</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="D8" s="42" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E8" s="43" t="s">
-        <x:v>79</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F8" s="44" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6" ht="28" customHeight="1">
       <x:c r="A9" s="33" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B9" s="34" t="s">
-        <x:v>92</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C9" s="35" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D9" s="36" t="s">
-        <x:v>74</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E9" s="37" t="s">
-        <x:v>75</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F9" s="45" t="s">
-        <x:v>159</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6" ht="28" customHeight="1">
       <x:c r="A10" s="39" t="s">
-        <x:v>126</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B10" s="40" t="s">
-        <x:v>92</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C10" s="41" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D10" s="42" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E10" s="43" t="s">
-        <x:v>7</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F10" s="46" t="s">
-        <x:v>159</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6" ht="28" customHeight="1">
       <x:c r="A11" s="33" t="s">
-        <x:v>104</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B11" s="34" t="s">
-        <x:v>92</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C11" s="35" t="s">
-        <x:v>255</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D11" s="36" t="s">
-        <x:v>115</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="E11" s="37" t="s">
-        <x:v>29</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F11" s="38" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6" ht="28" customHeight="1">
       <x:c r="A12" s="39" t="s">
-        <x:v>60</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B12" s="40" t="s">
-        <x:v>92</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C12" s="41" t="s">
-        <x:v>256</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D12" s="42" t="s">
-        <x:v>218</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E12" s="43" t="s">
-        <x:v>29</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F12" s="44" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" ht="28" customHeight="1">
       <x:c r="A13" s="33" t="s">
-        <x:v>62</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B13" s="34" t="s">
-        <x:v>92</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C13" s="35" t="s">
-        <x:v>252</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="D13" s="36" t="s">
-        <x:v>105</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E13" s="37" t="s">
-        <x:v>203</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="F13" s="38" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" ht="28" customHeight="1">
       <x:c r="A14" s="139" t="s">
-        <x:v>193</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B14" s="139"/>
       <x:c r="C14" s="139"/>
@@ -5134,82 +5134,82 @@
     </x:row>
     <x:row r="15" spans="1:6" ht="28" customHeight="1">
       <x:c r="A15" s="33" t="s">
-        <x:v>66</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B15" s="38" t="s">
-        <x:v>110</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C15" s="35" t="s">
-        <x:v>201</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D15" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E15" s="37" t="s">
-        <x:v>77</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F15" s="38" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6" ht="28" customHeight="1">
       <x:c r="A16" s="39" t="s">
-        <x:v>239</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B16" s="44" t="s">
-        <x:v>110</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C16" s="41" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D16" s="42" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E16" s="43" t="s">
-        <x:v>198</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="F16" s="44" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" ht="28" customHeight="1">
       <x:c r="A17" s="33" t="s">
-        <x:v>237</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B17" s="38" t="s">
-        <x:v>110</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C17" s="35" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D17" s="36" t="s">
-        <x:v>234</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="E17" s="37" t="s">
-        <x:v>208</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F17" s="38" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6" ht="28" customHeight="1">
       <x:c r="A18" s="39" t="s">
-        <x:v>230</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B18" s="44" t="s">
-        <x:v>110</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C18" s="41" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D18" s="42" t="s">
-        <x:v>68</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E18" s="43" t="s">
-        <x:v>2</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F18" s="44" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6" ht="28" customHeight="1">
@@ -5217,144 +5217,144 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="B19" s="38" t="s">
-        <x:v>110</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C19" s="35" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D19" s="36" t="s">
-        <x:v>235</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="E19" s="37" t="s">
-        <x:v>3</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F19" s="38" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6" ht="28" customHeight="1">
       <x:c r="A20" s="39" t="s">
-        <x:v>225</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B20" s="44" t="s">
-        <x:v>110</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C20" s="41" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D20" s="42" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E20" s="43" t="s">
-        <x:v>236</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="F20" s="44" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6" ht="28" customHeight="1">
       <x:c r="A21" s="33" t="s">
-        <x:v>232</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B21" s="38" t="s">
-        <x:v>110</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C21" s="35" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D21" s="36" t="s">
-        <x:v>64</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E21" s="37" t="s">
-        <x:v>220</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="F21" s="38" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6" ht="28" customHeight="1">
       <x:c r="A22" s="39" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B22" s="44" t="s">
-        <x:v>110</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C22" s="41" t="s">
         <x:v>251</x:v>
       </x:c>
       <x:c r="D22" s="42" t="s">
-        <x:v>118</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E22" s="43" t="s">
-        <x:v>11</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F22" s="44" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6" ht="28" customHeight="1">
       <x:c r="A23" s="33" t="s">
-        <x:v>71</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="38" t="s">
-        <x:v>110</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C23" s="35" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D23" s="36" t="s">
-        <x:v>243</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E23" s="37" t="s">
-        <x:v>27</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F23" s="38" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6" ht="28" customHeight="1">
       <x:c r="A24" s="39" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B24" s="44" t="s">
-        <x:v>110</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C24" s="41" t="s">
-        <x:v>206</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D24" s="42" t="s">
-        <x:v>190</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E24" s="43" t="s">
-        <x:v>31</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F24" s="44" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6" ht="28" customHeight="1">
       <x:c r="A25" s="33" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B25" s="38" t="s">
-        <x:v>110</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C25" s="35" t="s">
-        <x:v>202</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D25" s="36" t="s">
-        <x:v>70</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E25" s="37" t="s">
-        <x:v>33</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F25" s="38" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6" ht="28" customHeight="1">
       <x:c r="A26" s="139" t="s">
-        <x:v>194</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B26" s="139"/>
       <x:c r="C26" s="139"/>
@@ -5364,42 +5364,42 @@
     </x:row>
     <x:row r="27" spans="1:6" ht="28" customHeight="1">
       <x:c r="A27" s="33" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B27" s="47" t="s">
-        <x:v>166</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C27" s="35" t="s">
-        <x:v>209</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D27" s="36" t="s">
-        <x:v>90</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="E27" s="37" t="s">
-        <x:v>9</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F27" s="38" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6" ht="28" customHeight="1">
       <x:c r="A28" s="39" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B28" s="48" t="s">
-        <x:v>166</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C28" s="41" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="D28" s="42" t="s">
-        <x:v>116</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E28" s="43" t="s">
-        <x:v>78</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F28" s="44" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6" ht="28" customHeight="1">
@@ -5407,104 +5407,104 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B29" s="47" t="s">
-        <x:v>166</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C29" s="35" t="s">
-        <x:v>214</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D29" s="36" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E29" s="37" t="s">
-        <x:v>10</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F29" s="45" t="s">
-        <x:v>159</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6" ht="28" customHeight="1">
       <x:c r="A30" s="39" t="s">
-        <x:v>185</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B30" s="48" t="s">
-        <x:v>166</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C30" s="41" t="s">
-        <x:v>214</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D30" s="42" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E30" s="43" t="s">
-        <x:v>196</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F30" s="46" t="s">
-        <x:v>159</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6" ht="28" customHeight="1">
       <x:c r="A31" s="33" t="s">
-        <x:v>47</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="47" t="s">
-        <x:v>166</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C31" s="35" t="s">
-        <x:v>240</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="D31" s="36" t="s">
-        <x:v>186</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E31" s="37" t="s">
-        <x:v>81</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F31" s="38" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6" ht="28" customHeight="1">
       <x:c r="A32" s="39" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B32" s="48" t="s">
-        <x:v>166</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C32" s="41" t="s">
-        <x:v>117</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D32" s="42" t="s">
-        <x:v>41</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E32" s="43" t="s">
-        <x:v>8</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F32" s="44" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6" ht="28" customHeight="1">
       <x:c r="A33" s="33" t="s">
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B33" s="47" t="s">
-        <x:v>166</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C33" s="35" t="s">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D33" s="36" t="s">
-        <x:v>238</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="E33" s="37" t="s">
-        <x:v>8</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F33" s="38" t="s">
-        <x:v>150</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6" ht="28" customHeight="1">
       <x:c r="A34" s="139" t="s">
-        <x:v>247</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B34" s="139"/>
       <x:c r="C34" s="139"/>
@@ -5514,62 +5514,62 @@
     </x:row>
     <x:row r="35" spans="1:6" ht="28" customHeight="1">
       <x:c r="A35" s="33" t="s">
-        <x:v>48</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B35" s="49" t="s">
-        <x:v>167</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C35" s="35" t="s">
-        <x:v>240</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="D35" s="36" t="s">
-        <x:v>67</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E35" s="37" t="s">
-        <x:v>26</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F35" s="45" t="s">
-        <x:v>159</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:6" ht="28" customHeight="1">
       <x:c r="A36" s="39" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="50" t="s">
-        <x:v>167</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C36" s="41" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D36" s="42" t="s">
-        <x:v>69</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E36" s="43" t="s">
-        <x:v>12</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F36" s="46" t="s">
-        <x:v>159</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6" ht="28" customHeight="1">
       <x:c r="A37" s="33" t="s">
-        <x:v>195</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B37" s="49" t="s">
-        <x:v>167</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C37" s="35" t="s">
-        <x:v>207</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D37" s="36" t="s">
-        <x:v>87</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E37" s="37" t="s">
-        <x:v>34</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F37" s="45" t="s">
-        <x:v>159</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
@@ -6033,7 +6033,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" s="56" t="s">
-        <x:v>94</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B1" s="127"/>
       <x:c r="C1" s="123"/>
@@ -6042,7 +6042,7 @@
       <x:c r="F1" s="123"/>
       <x:c r="G1" s="124"/>
       <x:c r="H1" s="56" t="s">
-        <x:v>146</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="I1" s="128"/>
       <x:c r="J1" s="124"/>
@@ -6050,7 +6050,7 @@
     </x:row>
     <x:row r="2" spans="1:11" ht="16" customHeight="1">
       <x:c r="A2" s="125" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="125"/>
       <x:c r="C2" s="125"/>
@@ -6065,7 +6065,7 @@
     </x:row>
     <x:row r="3" spans="1:11" ht="16" customHeight="1">
       <x:c r="A3" s="125" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="125"/>
       <x:c r="C3" s="125"/>
@@ -6080,7 +6080,7 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="16" customHeight="1">
       <x:c r="A4" s="125" t="s">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B4" s="125"/>
       <x:c r="C4" s="125"/>
@@ -6095,7 +6095,7 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="126" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B5" s="123"/>
       <x:c r="C5" s="123"/>
@@ -6110,51 +6110,51 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="16" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C6" s="31" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="E6" s="57" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F6" s="57" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G6" s="51" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H6" s="51" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I6" s="25" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="J6" s="30" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="B6" s="4" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="C6" s="31" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="E6" s="57" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F6" s="57" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="G6" s="51" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H6" s="51" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="I6" s="25" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="J6" s="30" t="s">
-        <x:v>168</x:v>
-      </x:c>
       <x:c r="K6" s="30" t="s">
-        <x:v>178</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="58" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B7" s="59" t="s">
-        <x:v>133</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C7" s="60" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D7" s="61" t="s">
-        <x:v>244</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="E7" s="62"/>
       <x:c r="F7" s="63"/>
@@ -6166,20 +6166,20 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="67" t="s">
-        <x:v>145</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B8" s="68" t="s">
-        <x:v>147</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C8" s="69"/>
       <x:c r="D8" s="70" t="s">
-        <x:v>103</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E8" s="71" t="s">
-        <x:v>157</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F8" s="72" t="s">
-        <x:v>170</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G8" s="73"/>
       <x:c r="H8" s="73"/>
@@ -6189,20 +6189,20 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="58" t="s">
-        <x:v>143</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B9" s="59" t="s">
-        <x:v>147</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C9" s="76"/>
       <x:c r="D9" s="61" t="s">
-        <x:v>50</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E9" s="77" t="s">
-        <x:v>157</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F9" s="78" t="s">
-        <x:v>174</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G9" s="64"/>
       <x:c r="H9" s="64"/>
@@ -6212,80 +6212,80 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="67" t="s">
-        <x:v>170</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B10" s="68" t="s">
-        <x:v>133</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C10" s="79" t="s">
-        <x:v>145</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D10" s="70" t="s">
-        <x:v>217</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E10" s="80"/>
       <x:c r="F10" s="72" t="s">
-        <x:v>148</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G10" s="73"/>
       <x:c r="H10" s="73"/>
       <x:c r="I10" s="81" t="s">
-        <x:v>163</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J10" s="75"/>
       <x:c r="K10" s="75"/>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="58" t="s">
-        <x:v>174</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B11" s="59" t="s">
-        <x:v>133</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C11" s="60" t="s">
-        <x:v>143</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D11" s="61" t="s">
-        <x:v>54</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E11" s="62"/>
       <x:c r="F11" s="78" t="s">
-        <x:v>148</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G11" s="82" t="s">
-        <x:v>57</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H11" s="64"/>
       <x:c r="I11" s="65"/>
       <x:c r="J11" s="83" t="s">
-        <x:v>66</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K11" s="66"/>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="67" t="s">
-        <x:v>148</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B12" s="68" t="s">
-        <x:v>133</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C12" s="79" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D12" s="70" t="s">
-        <x:v>52</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E12" s="80"/>
       <x:c r="F12" s="72" t="s">
-        <x:v>183</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G12" s="84" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H12" s="73"/>
       <x:c r="I12" s="74"/>
       <x:c r="J12" s="85" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K12" s="75"/>
     </x:row>
@@ -7694,7 +7694,7 @@
       <x:c r="K120" s="3"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51180553436279297" footer="0.51180553436279297"/>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51166665554046631" footer="0.51166665554046631"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -7720,7 +7720,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" s="96" t="s">
-        <x:v>94</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B1" s="133"/>
       <x:c r="C1" s="130"/>
@@ -7729,7 +7729,7 @@
       <x:c r="F1" s="130"/>
       <x:c r="G1" s="131"/>
       <x:c r="H1" s="96" t="s">
-        <x:v>146</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="I1" s="134"/>
       <x:c r="J1" s="131"/>
@@ -7737,7 +7737,7 @@
     </x:row>
     <x:row r="2" spans="1:11" ht="16" customHeight="1">
       <x:c r="A2" s="132" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="132"/>
       <x:c r="C2" s="132"/>
@@ -7752,7 +7752,7 @@
     </x:row>
     <x:row r="3" spans="1:11" ht="16" customHeight="1">
       <x:c r="A3" s="132" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="132"/>
       <x:c r="C3" s="132"/>
@@ -7767,7 +7767,7 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="16" customHeight="1">
       <x:c r="A4" s="132" t="s">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B4" s="132"/>
       <x:c r="C4" s="132"/>
@@ -7782,7 +7782,7 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="129" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B5" s="130"/>
       <x:c r="C5" s="130"/>
@@ -7797,76 +7797,74 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="97" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B6" s="98" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C6" s="99" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D6" s="100" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="E6" s="101" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F6" s="101" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G6" s="102" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H6" s="102" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I6" s="103" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="J6" s="104" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="B6" s="98" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="C6" s="99" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D6" s="100" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="E6" s="101" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F6" s="101" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="G6" s="102" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H6" s="102" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="I6" s="103" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="J6" s="104" t="s">
-        <x:v>168</x:v>
-      </x:c>
       <x:c r="K6" s="104" t="s">
-        <x:v>178</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="105" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B7" s="106" t="s">
-        <x:v>177</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C7" s="107" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D7" s="108" t="s">
-        <x:v>89</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E7" s="114"/>
       <x:c r="F7" s="115"/>
       <x:c r="G7" s="118"/>
       <x:c r="H7" s="118"/>
       <x:c r="I7" s="122"/>
-      <x:c r="J7" s="7" t="s">
-        <x:v>126</x:v>
-      </x:c>
+      <x:c r="J7" s="7"/>
       <x:c r="K7" s="119" t="s">
-        <x:v>136</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="109" t="s">
-        <x:v>145</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B8" s="110" t="s">
-        <x:v>136</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C8" s="116" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D8" s="111" t="s">
-        <x:v>32</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E8" s="112"/>
       <x:c r="F8" s="113"/>
@@ -7878,20 +7876,20 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="105" t="s">
-        <x:v>143</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B9" s="106" t="s">
-        <x:v>147</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C9" s="107"/>
       <x:c r="D9" s="108" t="s">
-        <x:v>109</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E9" s="114" t="s">
-        <x:v>157</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F9" s="115" t="s">
-        <x:v>181</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G9" s="118"/>
       <x:c r="H9" s="118"/>
@@ -7901,16 +7899,16 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="109" t="s">
-        <x:v>181</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B10" s="110" t="s">
-        <x:v>136</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C10" s="116" t="s">
-        <x:v>143</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D10" s="111" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E10" s="112"/>
       <x:c r="F10" s="113"/>
@@ -7922,16 +7920,16 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="105" t="s">
-        <x:v>176</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B11" s="106" t="s">
-        <x:v>136</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C11" s="107" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D11" s="108" t="s">
-        <x:v>76</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E11" s="114"/>
       <x:c r="F11" s="115"/>
@@ -7943,20 +7941,20 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="109" t="s">
-        <x:v>180</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B12" s="110" t="s">
-        <x:v>147</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C12" s="116"/>
       <x:c r="D12" s="111" t="s">
-        <x:v>88</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="E12" s="112" t="s">
-        <x:v>157</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F12" s="113" t="s">
-        <x:v>171</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G12" s="120"/>
       <x:c r="H12" s="120"/>
@@ -7966,16 +7964,16 @@
     </x:row>
     <x:row r="13" spans="1:11" ht="18" customHeight="1">
       <x:c r="A13" s="17" t="s">
-        <x:v>171</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B13" s="86" t="s">
-        <x:v>136</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C13" s="87" t="s">
-        <x:v>143</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D13" s="88" t="s">
-        <x:v>254</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="E13" s="89"/>
       <x:c r="F13" s="90"/>
@@ -7987,39 +7985,37 @@
     </x:row>
     <x:row r="14" spans="1:11" ht="18" customHeight="1">
       <x:c r="A14" s="20" t="s">
-        <x:v>182</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B14" s="91" t="s">
-        <x:v>136</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C14" s="92" t="s">
-        <x:v>145</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D14" s="93" t="s">
-        <x:v>189</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E14" s="94"/>
       <x:c r="F14" s="95"/>
       <x:c r="G14" s="54"/>
       <x:c r="H14" s="54"/>
       <x:c r="I14" s="29"/>
-      <x:c r="J14" s="7" t="s">
-        <x:v>53</x:v>
-      </x:c>
+      <x:c r="J14" s="7"/>
       <x:c r="K14" s="121"/>
     </x:row>
     <x:row r="15" spans="1:11" ht="18" customHeight="1">
       <x:c r="A15" s="17" t="s">
-        <x:v>169</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B15" s="86" t="s">
-        <x:v>136</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C15" s="87" t="s">
-        <x:v>152</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D15" s="88" t="s">
-        <x:v>192</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E15" s="89"/>
       <x:c r="F15" s="90"/>
@@ -8031,16 +8027,16 @@
     </x:row>
     <x:row r="16" spans="1:11" ht="18" customHeight="1">
       <x:c r="A16" s="20" t="s">
-        <x:v>170</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B16" s="91" t="s">
-        <x:v>136</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C16" s="92" t="s">
-        <x:v>143</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D16" s="93" t="s">
-        <x:v>187</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E16" s="94"/>
       <x:c r="F16" s="95"/>
@@ -9403,7 +9399,7 @@
       <x:c r="K120" s="3"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51180553436279297" footer="0.51180553436279297"/>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51166665554046631" footer="0.51166665554046631"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>